--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,40 +530,45 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>emergency_fill</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -572,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>hQiNHHd2</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.8125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,74 +610,77 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3442622950819672</v>
+        <v>0.4203657594230275</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2254098360655738</v>
+        <v>0.2658195243410321</v>
       </c>
       <c r="N2" t="n">
-        <v>0.430327868852459</v>
+        <v>0.3138147162359406</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05627705627705626</v>
+        <v>0.1064561483508131</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3171981931068084</v>
+        <v>0.2941043770124148</v>
       </c>
       <c r="R2" t="n">
-        <v>0.09734605233779631</v>
+        <v>0.2412483660587597</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5854557545553953</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0.1551278857029363</v>
-      </c>
+        <v>0.4646472569288255</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>0.1508325406928849</v>
+      </c>
+      <c r="W2" t="n">
         <v>2</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.1551278857029363</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.5854557545553953</v>
+        <v>0.1508325406928849</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z2" t="inlineStr">
+        <v>0.4646472569288255</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>24.27278772776977</v>
-      </c>
       <c r="AB2" t="n">
-        <v>24.27278772776977</v>
+        <v>13.93941770786476</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13.93941770786476</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
+          <t>C6QBlj7R</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -681,7 +689,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,83 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4540461369461735</v>
+        <v>0.4015444015444015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2383742218967411</v>
+        <v>0.250965250965251</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3075796411570853</v>
+        <v>0.3474903474903475</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04877112135176653</v>
+        <v>0.1068376068376069</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3952923866051036</v>
+        <v>0.338465551898858</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3647683548218201</v>
+        <v>0.2229663567343241</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2399392585730763</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>-0.05875375034106994</v>
-      </c>
+        <v>0.438568091366818</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0.0910777438764705</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.05875375034106994</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3952923866051036</v>
+        <v>0.0910777438764705</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+        <v>0.438568091366818</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA3" t="n">
-        <v>14.76461933025518</v>
-      </c>
       <c r="AB3" t="n">
-        <v>14.76461933025518</v>
+        <v>13.15704274100454</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.15704274100454</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>dbI3Q902</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,78 +808,81 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5129935875801552</v>
+        <v>0.3983286908077994</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2372595342558218</v>
+        <v>0.2757660167130919</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2497468781640229</v>
+        <v>0.3259052924791086</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05369843527738261</v>
+        <v>0.1157731157731159</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5651107829134597</v>
+        <v>0.3251752008041984</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3272216985544737</v>
+        <v>0.2145549362801127</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1076675185320665</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="n">
-        <v>0.0521171953333045</v>
-      </c>
+        <v>0.4602698629156889</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0.1343645704365803</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0521171953333045</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5651107829134597</v>
+        <v>0.1343645704365803</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z4" t="inlineStr">
+        <v>0.4602698629156889</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA4" t="n">
-        <v>23.25553914567299</v>
-      </c>
       <c r="AB4" t="n">
-        <v>23.25553914567299</v>
+        <v>13.80809588747067</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>13.80809588747067</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
+          <t>zkH7PTF8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -893,78 +907,81 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.483021608861449</v>
+        <v>0.4482173174872666</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2478663519157435</v>
+        <v>0.2716468590831919</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2691120392228073</v>
+        <v>0.2801358234295416</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06169269327164084</v>
+        <v>0.115530303030303</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5744780353398029</v>
+        <v>0.3229062020104645</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1582272001885582</v>
+        <v>0.2504209781479554</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2672947644716389</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>0.09145642647835389</v>
-      </c>
+        <v>0.4266728198415802</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0.1465369964120385</v>
       </c>
       <c r="W5" t="n">
-        <v>0.09145642647835389</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5744780353398029</v>
+        <v>0.1465369964120385</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+        <v>0.4266728198415802</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA5" t="n">
-        <v>23.72390176699015</v>
-      </c>
       <c r="AB5" t="n">
-        <v>23.72390176699015</v>
+        <v>12.8001845952474</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12.8001845952474</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
+          <t>UPVAOmVE</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -989,83 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5190138736400838</v>
+        <v>0.3621033947193255</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2435372791695778</v>
+        <v>0.282893277124473</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2374488471903384</v>
+        <v>0.3550033281562015</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05285834384195032</v>
+        <v>0.1046568627450981</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4270633323371791</v>
+        <v>0.5367918914801082</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2503592251123753</v>
+        <v>0.1988035637597261</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3225774425504456</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>-0.09195054130290464</v>
-      </c>
+        <v>0.2644045447601658</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0.1746884967607827</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.09195054130290464</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4270633323371791</v>
+        <v>0.1746884967607827</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z6" t="inlineStr">
+        <v>0.5367918914801082</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA6" t="n">
-        <v>16.35316661685896</v>
-      </c>
       <c r="AB6" t="n">
-        <v>16.35316661685896</v>
+        <v>16.10375674440325</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>16.10375674440325</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>8GUEN7pL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,74 +1105,77 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="J7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.9</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.486111111111111</v>
+        <v>0.5523316062176166</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2430555555555555</v>
+        <v>0.2182383419689119</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2294300518134715</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05494505494505519</v>
+        <v>0.1175966460519307</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5439950475586786</v>
+        <v>0.3448457054801212</v>
       </c>
       <c r="R7" t="n">
-        <v>0.254427650280188</v>
+        <v>0.2257559088833044</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2015773021611334</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="n">
-        <v>0.05788393644756751</v>
-      </c>
+        <v>0.4293983856365744</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0.1999683338231029</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05788393644756751</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5439950475586786</v>
+        <v>0.1999683338231029</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+        <v>0.4293983856365744</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA7" t="n">
-        <v>22.19975237793393</v>
-      </c>
       <c r="AB7" t="n">
-        <v>22.19975237793393</v>
+        <v>12.88195156909723</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12.88195156909723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>juKJMRaR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45493.85416666666</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1161,7 +1184,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1181,83 +1204,86 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5804311774461028</v>
+        <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2280265339966833</v>
+        <v>0.24</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1915422885572139</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04415584415584406</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5007784001595581</v>
+        <v>0.3602133911507752</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4077788553508637</v>
+        <v>0.2642295501804442</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09144274448957818</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
-        <v>-0.07965277728654474</v>
-      </c>
+        <v>0.3755570586687805</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>-0.02444294133121944</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.07965277728654474</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5007784001595581</v>
+        <v>-0.02444294133121944</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z8" t="inlineStr">
+        <v>0.3755570586687805</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>20.0389200079779</v>
-      </c>
       <c r="AB8" t="n">
-        <v>20.0389200079779</v>
+        <v>11.26671176006342</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.26671176006342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45493.89583333334</v>
+        <v>45528.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1277,85 +1303,86 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3787575150300601</v>
+        <v>0.375</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2705410821643286</v>
+        <v>0.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3507014028056112</v>
+        <v>0.375</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05608465608465618</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3059042849263034</v>
+        <v>0.286973223304776</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2411412109970197</v>
+        <v>0.2020046864320479</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4529545040766769</v>
+        <v>0.511022090263176</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.1022531012710657</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.136022090263176</v>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="W9" t="n">
-        <v>0.1022531012710657</v>
-      </c>
       <c r="X9" t="n">
-        <v>0.4529545040766769</v>
+        <v>0.136022090263176</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z9" t="inlineStr">
+        <v>0.511022090263176</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>17.64772520383385</v>
-      </c>
       <c r="AB9" t="n">
-        <v>17.64772520383385</v>
+        <v>15.33066270789528</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>15.33066270789528</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45493.89583333334</v>
+        <v>45528.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1375,85 +1402,86 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="J10" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6020278833967048</v>
+        <v>0.4615701627859057</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1989860583016477</v>
+        <v>0.2571605192664331</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1989860583016477</v>
+        <v>0.2812693179476612</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05799530673818287</v>
+        <v>0.1110347985347986</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.278032638556221</v>
+        <v>0.4120850349593068</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1727465748734516</v>
+        <v>0.2718004932686233</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5492207865703275</v>
+        <v>0.3161144717720697</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.3502347282686798</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>-0.04948512782659886</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3502347282686798</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5492207865703275</v>
+        <v>-0.04948512782659886</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Z10" t="inlineStr">
+        <v>0.4120850349593068</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA10" t="n">
-        <v>22.46103932851637</v>
-      </c>
       <c r="AB10" t="n">
-        <v>22.46103932851637</v>
+        <v>12.3625510487792</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12.3625510487792</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45493.89583333334</v>
+        <v>45528.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1473,85 +1501,86 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4698795180722892</v>
+        <v>0.3986856516976999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2409638554216868</v>
+        <v>0.2562979189485213</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2891566265060241</v>
+        <v>0.3450164293537787</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0641025641025641</v>
+        <v>0.1147741147741148</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3544309155237736</v>
+        <v>0.4053460663506484</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2227510400406634</v>
+        <v>0.213679266275626</v>
       </c>
       <c r="S11" t="n">
-        <v>0.422818044435563</v>
+        <v>0.3809746673737255</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0.1336614179295388</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>0.006660414652948532</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1336614179295388</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.422818044435563</v>
+        <v>0.006660414652948532</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z11" t="inlineStr">
+        <v>0.4053460663506484</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA11" t="n">
-        <v>16.14090222177815</v>
-      </c>
       <c r="AB11" t="n">
-        <v>16.14090222177815</v>
+        <v>12.16038199051945</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12.16038199051945</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>69kBKJCq</t>
+          <t>S0BoIo8r</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45493.9375</v>
+        <v>45528.89583333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1571,85 +1600,86 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4689603590127151</v>
+        <v>0.375</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2468212415856395</v>
+        <v>0.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2842183994016455</v>
+        <v>0.375</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06618819776714502</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2638376359246903</v>
+        <v>0.1977260679167301</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2365134786384609</v>
+        <v>0.2623609146748476</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4996488854368489</v>
+        <v>0.5399130174084223</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0.2154304860352034</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
+        <v>0.1649130174084223</v>
+      </c>
+      <c r="W12" t="n">
         <v>2</v>
       </c>
-      <c r="W12" t="n">
-        <v>0.2154304860352034</v>
-      </c>
       <c r="X12" t="n">
-        <v>0.4996488854368489</v>
+        <v>0.1649130174084223</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z12" t="inlineStr">
+        <v>0.5399130174084223</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA12" t="n">
-        <v>19.98244427184244</v>
-      </c>
       <c r="AB12" t="n">
-        <v>19.98244427184244</v>
+        <v>16.19739052225267</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>16.19739052225267</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45493.97916666666</v>
+        <v>45528.9375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1669,85 +1699,86 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.5866460825935932</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2243921265920494</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.1889617908143573</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.1141210870313039</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3588342128344589</v>
+        <v>0.375225216838503</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1782778900516307</v>
+        <v>0.2475974238107352</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4628878971139105</v>
+        <v>0.3771773593507619</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0.1660490382087447</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
+        <v>0.1882155685364045</v>
+      </c>
+      <c r="W13" t="n">
         <v>2</v>
       </c>
-      <c r="W13" t="n">
-        <v>0.1660490382087447</v>
-      </c>
       <c r="X13" t="n">
-        <v>0.4628878971139105</v>
+        <v>0.1882155685364045</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z13" t="inlineStr">
+        <v>0.3771773593507619</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA13" t="n">
-        <v>18.14439485569552</v>
-      </c>
       <c r="AB13" t="n">
-        <v>18.14439485569552</v>
+        <v>11.31532078052286</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11.31532078052286</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MHXbihN8</t>
+          <t>Ik4bFqh1</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45493.97916666666</v>
+        <v>45528.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1767,85 +1798,86 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4308880308880309</v>
+        <v>0.5614973262032086</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2633204633204634</v>
+        <v>0.2245989304812834</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3057915057915058</v>
+        <v>0.213903743315508</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05490387748452252</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4648599986654099</v>
+        <v>0.4597878939037249</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1333223620980795</v>
+        <v>0.2646164299276401</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4018176392365106</v>
+        <v>0.2755956761686351</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.03397196777737899</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>-0.1017094322994837</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03397196777737899</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4648599986654099</v>
+        <v>-0.1017094322994837</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z14" t="inlineStr">
+        <v>0.4597878939037249</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA14" t="n">
-        <v>18.24299993327049</v>
-      </c>
       <c r="AB14" t="n">
-        <v>18.24299993327049</v>
+        <v>13.79363681711175</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13.79363681711175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>p0lFJwSk</t>
+          <t>dt32E377</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45493.98958333334</v>
+        <v>45528.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1865,66 +1897,67 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4947263544851754</v>
+        <v>0.4992272024729521</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2099838526814855</v>
+        <v>0.2642967542503864</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2952897928333391</v>
+        <v>0.2364760432766615</v>
       </c>
       <c r="O15" t="n">
-        <v>0.05828243164630598</v>
+        <v>0.1128310973512212</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3290979258065211</v>
+        <v>0.5036562389831492</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2519301582287538</v>
+        <v>0.2267771889194808</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4189719159647251</v>
+        <v>0.2695665720973701</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0.123682123131386</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0.004429036510197049</v>
       </c>
       <c r="W15" t="n">
-        <v>0.123682123131386</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4189719159647251</v>
+        <v>0.004429036510197049</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z15" t="inlineStr">
+        <v>0.5036562389831492</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AA15" t="n">
-        <v>15.94859579823625</v>
-      </c>
       <c r="AB15" t="n">
-        <v>15.94859579823625</v>
+        <v>15.10968716949447</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>15.10968716949447</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,15 +577,15 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.8125</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4203657594230275</v>
+        <v>0.5125</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2658195243410321</v>
+        <v>0.25625</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3138147162359406</v>
+        <v>0.23125</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1064561483508131</v>
+        <v>0.05471324983520098</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2941043770124148</v>
+        <v>0.3377402916227287</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2412483660587597</v>
+        <v>0.2044732780367439</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4646472569288255</v>
+        <v>0.4577864303405274</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1508325406928849</v>
+        <v>0.2265364303405274</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1508325406928849</v>
+        <v>0.2265364303405274</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4646472569288255</v>
+        <v>0.4577864303405274</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>13.93941770786476</v>
+        <v>4.917977593205657</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.93941770786476</v>
+        <v>4.917977593205657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4015444015444015</v>
+        <v>0.4339848424411648</v>
       </c>
       <c r="M3" t="n">
-        <v>0.250965250965251</v>
+        <v>0.2744315915436777</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3474903474903475</v>
+        <v>0.2915835660151576</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1068376068376069</v>
+        <v>0.07173392612859097</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.338465551898858</v>
+        <v>0.4198727351394672</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2229663567343241</v>
+        <v>0.2341574162512325</v>
       </c>
       <c r="S3" t="n">
-        <v>0.438568091366818</v>
+        <v>0.3459698486093002</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.0910777438764705</v>
+        <v>-0.01411210730169754</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0910777438764705</v>
+        <v>-0.01411210730169754</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.438568091366818</v>
+        <v>0.4198727351394672</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>13.15704274100454</v>
+        <v>3.577573005304107</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.15704274100454</v>
+        <v>3.577573005304107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3983286908077994</v>
+        <v>0.5816922989614663</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2757660167130919</v>
+        <v>0.2298393961750184</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3259052924791086</v>
+        <v>0.1884683048635151</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1157731157731159</v>
+        <v>0.06118638964167422</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3251752008041984</v>
+        <v>0.4708662451903216</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2145549362801127</v>
+        <v>0.2579888991870886</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4602698629156889</v>
+        <v>0.2711448556225899</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1343645704365803</v>
+        <v>-0.1108260537711447</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1343645704365803</v>
+        <v>-0.1108260537711447</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4602698629156889</v>
+        <v>0.4708662451903216</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>13.80809588747067</v>
+        <v>3.174457996355339</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.80809588747067</v>
+        <v>3.174457996355339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>dc united</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -910,83 +910,83 @@
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4482173174872666</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2716468590831919</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2801358234295416</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="O5" t="n">
-        <v>0.115530303030303</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3229062020104645</v>
+        <v>0.3514815284390531</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2504209781479554</v>
+        <v>0.3117912772958937</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4266728198415802</v>
+        <v>0.3367271942650532</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1465369964120385</v>
+        <v>-0.1186677252922902</v>
       </c>
       <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.1186677252922902</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.3514815284390531</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2</v>
       </c>
-      <c r="X5" t="n">
-        <v>0.1465369964120385</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.4266728198415802</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>12.8001845952474</v>
+        <v>2.052708716068566</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.8001845952474</v>
+        <v>2.052708716068566</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3621033947193255</v>
+        <v>0.4339765418085509</v>
       </c>
       <c r="M6" t="n">
-        <v>0.282893277124473</v>
+        <v>0.2580401059402194</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3550033281562015</v>
+        <v>0.3079833522512297</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1046568627450981</v>
+        <v>0.04739636997701502</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5367918914801082</v>
+        <v>0.239359255323122</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1988035637597261</v>
+        <v>0.183496600686781</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2644045447601658</v>
+        <v>0.5771441439900971</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1746884967607827</v>
+        <v>0.2691607917388674</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1746884967607827</v>
+        <v>0.2691607917388674</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5367918914801082</v>
+        <v>0.5771441439900971</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>16.10375674440325</v>
+        <v>5.970349127139315</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.10375674440325</v>
+        <v>5.970349127139315</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,859 +1105,67 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5523316062176166</v>
+        <v>0.4830216088614491</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2182383419689119</v>
+        <v>0.2691120392228074</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2294300518134715</v>
+        <v>0.2478663519157436</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1175966460519307</v>
+        <v>0.06169269327164062</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3448457054801212</v>
+        <v>0.4579211748177075</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2257559088833044</v>
+        <v>0.2409446874376249</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4293983856365744</v>
+        <v>0.3011341377446677</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1999683338231029</v>
+        <v>-0.02510043404374163</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1999683338231029</v>
+        <v>-0.02510043404374163</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4293983856365744</v>
+        <v>0.4579211748177075</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>12.88195156909723</v>
+        <v>3.816160790612154</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.88195156909723</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>columbus crew</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>167</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.1111111111111112</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.3602133911507752</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.2642295501804442</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.3755570586687805</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>-0.02444294133121944</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.02444294133121944</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.3755570586687805</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>11.26671176006342</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.26671176006342</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>167</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.1111111111111112</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.286973223304776</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.2020046864320479</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.511022090263176</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.136022090263176</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.136022090263176</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.511022090263176</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>15.33066270789528</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>15.33066270789528</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>167</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.4615701627859057</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2571605192664331</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2812693179476612</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.1110347985347986</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.4120850349593068</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.2718004932686233</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3161144717720697</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>-0.04948512782659886</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.04948512782659886</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4120850349593068</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>12.3625510487792</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>12.3625510487792</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>167</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.3986856516976999</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2562979189485213</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.3450164293537787</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.1147741147741148</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.4053460663506484</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.213679266275626</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.3809746673737255</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>0.006660414652948532</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.006660414652948532</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.4053460663506484</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>12.16038199051945</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12.16038199051945</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.1111111111111112</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.1977260679167301</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.2623609146748476</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.5399130174084223</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.1649130174084223</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.1649130174084223</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.5399130174084223</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>16.19739052225267</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>16.19739052225267</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45528.9375</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>167</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.5866460825935932</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2243921265920494</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1889617908143573</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.1141210870313039</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.375225216838503</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2475974238107352</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.3771773593507619</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>0.1882155685364045</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.1882155685364045</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.3771773593507619</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>11.31532078052286</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.31532078052286</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>167</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5614973262032086</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2245989304812834</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.213903743315508</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.1130952380952381</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.4597878939037249</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.2646164299276401</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.2755956761686351</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.1017094322994837</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.1017094322994837</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4597878939037249</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>13.79363681711175</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>13.79363681711175</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>167</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.4992272024729521</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2642967542503864</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2364760432766615</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.1128310973512212</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5036562389831492</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.2267771889194808</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2695665720973701</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.004429036510197049</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.004429036510197049</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.5036562389831492</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>15.10968716949447</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>15.10968716949447</v>
+        <v>3.816160790612154</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,29 +634,29 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3377402916227287</v>
+        <v>0.3497608617534901</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2044732780367439</v>
+        <v>0.21545903665959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4577864303405274</v>
+        <v>0.43478010158692</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2265364303405274</v>
+        <v>0.2035301015869199</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2265364303405274</v>
+        <v>0.2035301015869199</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4577864303405274</v>
+        <v>0.43478010158692</v>
       </c>
       <c r="Z2" t="n">
         <v>4.1</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.917977593205657</v>
+        <v>5.3478010158692</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.917977593205657</v>
+        <v>5.3478010158692</v>
       </c>
     </row>
     <row r="3">
@@ -715,47 +715,47 @@
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4339848424411648</v>
+        <v>0.4299408525392617</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2744315915436777</v>
+        <v>0.2718743626351214</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2915835660151576</v>
+        <v>0.298184784825617</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07173392612859097</v>
+        <v>0.08181457128988123</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4198727351394672</v>
+        <v>0.405368832637219</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2341574162512325</v>
+        <v>0.2303900953091553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3459698486093002</v>
+        <v>0.3642410720536257</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.01411210730169754</v>
+        <v>-0.02457201990204272</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01411210730169754</v>
+        <v>-0.02457201990204272</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4198727351394672</v>
+        <v>0.405368832637219</v>
       </c>
       <c r="Z3" t="n">
         <v>2.15</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.577573005304107</v>
+        <v>3.807968127351762</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.577573005304107</v>
+        <v>3.807968127351762</v>
       </c>
     </row>
     <row r="4">
@@ -832,29 +832,29 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4708662451903216</v>
+        <v>0.4762889599790953</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2579888991870886</v>
+        <v>0.2714879806671771</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2711448556225899</v>
+        <v>0.2522230593537277</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1108260537711447</v>
+        <v>-0.105403338982371</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1108260537711447</v>
+        <v>-0.105403338982371</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4708662451903216</v>
+        <v>0.4762889599790953</v>
       </c>
       <c r="Z4" t="n">
         <v>1.62</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.174457996355339</v>
+        <v>3.708856209967243</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.174457996355339</v>
+        <v>3.708856209967243</v>
       </c>
     </row>
     <row r="5">
@@ -910,53 +910,53 @@
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.4664634146341463</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.0718954248366015</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3514815284390531</v>
+        <v>0.3342268665702494</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3117912772958937</v>
+        <v>0.3090746716112626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3367271942650532</v>
+        <v>0.3566984618184881</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1186677252922902</v>
+        <v>0.09755212035507349</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1186677252922902</v>
+        <v>0.09755212035507349</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3514815284390531</v>
+        <v>0.3566984618184881</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.052708716068566</v>
+        <v>4.542505821735616</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.052708716068566</v>
+        <v>4.542505821735616</v>
       </c>
     </row>
     <row r="6">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4339765418085509</v>
+        <v>0.4652011310772599</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2580401059402194</v>
+        <v>0.2543099516555687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3079833522512297</v>
+        <v>0.2804889172671714</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04739636997701502</v>
+        <v>0.04858919177427068</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.239359255323122</v>
+        <v>0.2361055348521834</v>
       </c>
       <c r="R6" t="n">
-        <v>0.183496600686781</v>
+        <v>0.1870163382524981</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5771441439900971</v>
+        <v>0.5768781268953186</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2691607917388674</v>
+        <v>0.2963892096281472</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2691607917388674</v>
+        <v>0.2963892096281472</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5771441439900971</v>
+        <v>0.5768781268953186</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.970349127139315</v>
+        <v>6.768781268953186</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.970349127139315</v>
+        <v>6.768781268953186</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4830216088614491</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2691120392228074</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2478663519157436</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06169269327164062</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4579211748177075</v>
+        <v>0.4671026151227732</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2409446874376249</v>
+        <v>0.260227184233846</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3011341377446677</v>
+        <v>0.2726702006433806</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.02510043404374163</v>
+        <v>0.006779185261923337</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.02510043404374163</v>
+        <v>0.006779185261923337</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4579211748177075</v>
+        <v>0.4671026151227732</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,1297 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.816160790612154</v>
+        <v>4.738818003846966</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.816160790612154</v>
+        <v>4.738818003846966</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5140066820868672</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2508352608583912</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2351580570547417</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06311475409836054</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3893485902148922</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2022707830121813</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4083806267729265</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1732225697181847</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1732225697181847</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4083806267729265</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.083806267729265</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.083806267729265</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3011272141706924</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2745571658615137</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4243156199677939</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.07124374676556844</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3106289633555401</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2355361087374685</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4538349279069915</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.02951930793919766</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.02951930793919766</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4538349279069915</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.833542358461892</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.833542358461892</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2765957446808511</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06334841628959276</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3080356206582852</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2195141922165861</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4724501871251287</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1107480594655543</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1107480594655543</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4724501871251287</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.724501871251287</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.724501871251287</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3765084473049075</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2614641995172969</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3620273531777956</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06239316239316239</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3125887724568495</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2433196768276677</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4440915507154829</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.08206419753768729</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.08206419753768729</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4440915507154829</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.261557482531702</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.261557482531702</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5198358413132695</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2462380300957592</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2339261285909713</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06871345029239762</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4248118716481093</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2198265310827618</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3553615972691289</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.09502396966516025</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.09502396966516025</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4248118716481093</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.29787901982949</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.29787901982949</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5731605711494815</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2265348924066998</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2003045364438188</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05103119243892862</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.5180211694488097</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2243435086214475</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2576353219297429</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.05513940170067178</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.05513940170067178</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5180211694488097</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.628817677481379</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.628817677481379</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4701492537313433</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2611940298507463</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3797271155273778</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2746597043437124</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3456131801289099</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.09042213820396555</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.09042213820396555</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3797271155273778</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.893049773234122</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.893049773234122</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3411167512690355</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2680203045685279</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3908629441624366</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06601731601731609</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3150329656153589</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2351641989709528</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4498028354136882</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.05893989125125165</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.05893989125125165</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4498028354136882</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.087427266649398</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.087427266649398</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4586948321388156</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2474537910222558</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2938513768389287</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06346277278562251</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3161732858012471</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2199821613977584</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4638445528009945</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1699931759620658</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1699931759620658</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4638445528009945</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.638445528009946</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.638445528009946</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4605263157894737</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2697368421052631</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2697368421052631</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0592334494773521</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.299676077465786</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1938962583852312</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5064276641489829</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2366908220437198</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2366908220437198</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5064276641489829</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>6.064276641489829</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.064276641489829</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.9375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4160475482912332</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.24962852897474</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3343239227340268</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06825396825396823</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1779266173323399</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2052194510738222</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6168539315938379</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.2825300088598112</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.2825300088598112</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6168539315938379</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.168539315938379</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.168539315938379</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3620273531777956</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2614641995172969</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3765084473049075</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06239316239316239</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3629192028742917</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2002684583220724</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.436812338803636</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.06030389149872845</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.06030389149872845</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.436812338803636</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.971162303023644</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.971162303023644</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6516432743439978</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2039926771859472</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1443640484700549</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06568190263842455</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.3763672115475741</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2687075571057277</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3549252313466982</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.2752760627964237</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.2752760627964237</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.623632788452426</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.693693693693694</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.236327884524259</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.236327884524259</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>A3m1Vera</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5125</v>
+        <v>0.5496329396744335</v>
       </c>
       <c r="M2" t="n">
-        <v>0.25625</v>
+        <v>0.2278965847430578</v>
       </c>
       <c r="N2" t="n">
-        <v>0.23125</v>
+        <v>0.2224704755825088</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05471324983520098</v>
+        <v>0.07023297123727534</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3497608617534901</v>
+        <v>0.4064475107721597</v>
       </c>
       <c r="R2" t="n">
-        <v>0.21545903665959</v>
+        <v>0.2317732046264059</v>
       </c>
       <c r="S2" t="n">
-        <v>0.43478010158692</v>
+        <v>0.3617792846014344</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2035301015869199</v>
+        <v>-0.1431854289022738</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2035301015869199</v>
+        <v>-0.1431854289022738</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.43478010158692</v>
+        <v>0.4064475107721597</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.3478010158692</v>
+        <v>21.29386012878101</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.3478010158692</v>
+        <v>21.29386012878101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>8lOY3V6E</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4299408525392617</v>
+        <v>0.3452849740932643</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2718743626351214</v>
+        <v>0.2741968911917099</v>
       </c>
       <c r="N3" t="n">
-        <v>0.298184784825617</v>
+        <v>0.3805181347150259</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08181457128988123</v>
+        <v>0.07265128273531629</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.405368832637219</v>
+        <v>0.2468291676521915</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2303900953091553</v>
+        <v>0.2218764908215194</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3642410720536257</v>
+        <v>0.5312943415262892</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.02457201990204272</v>
+        <v>0.1507762068112633</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.02457201990204272</v>
+        <v>0.1507762068112633</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.405368832637219</v>
+        <v>0.5312943415262892</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.807968127351762</v>
+        <v>51.06201893212862</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.807968127351762</v>
+        <v>51.06201893212862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>ITj9TZCB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5816922989614663</v>
+        <v>0.3752547900529964</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2298393961750184</v>
+        <v>0.2680391357521402</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1884683048635151</v>
+        <v>0.3567060741948635</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06118638964167422</v>
+        <v>0.06594242259641492</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4762889599790953</v>
+        <v>0.3418456284354434</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2714879806671771</v>
+        <v>0.2452920074904522</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2522230593537277</v>
+        <v>0.4128623640741045</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.105403338982371</v>
+        <v>0.05615628987924098</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.105403338982371</v>
+        <v>0.05615628987924098</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4762889599790953</v>
+        <v>0.4128623640741045</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.708856209967243</v>
+        <v>37.93640749224091</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.708856209967243</v>
+        <v>37.93640749224091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>lfn5UFc5</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45542.89583333334</v>
+        <v>45549.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,86 +907,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4664634146341463</v>
+        <v>0.4174185955276579</v>
       </c>
       <c r="M5" t="n">
-        <v>0.274390243902439</v>
+        <v>0.2471557473519027</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2591463414634146</v>
+        <v>0.3354256571204394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0718954248366015</v>
+        <v>0.06474519632414366</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3342268665702494</v>
+        <v>0.3110030730157736</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3090746716112626</v>
+        <v>0.2983757453433368</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3566984618184881</v>
+        <v>0.3906211816408898</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09755212035507349</v>
+        <v>0.05519552452045035</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09755212035507349</v>
+        <v>0.05519552452045035</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3566984618184881</v>
+        <v>0.3906211816408898</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.542505821735616</v>
+        <v>36.05972617342332</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.542505821735616</v>
+        <v>36.05972617342332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>dKkDSgSH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45542.89583333334</v>
+        <v>45549.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4652011310772599</v>
+        <v>0.6221653026800774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2543099516555687</v>
+        <v>0.215530705316424</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2804889172671714</v>
+        <v>0.1623039920034985</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04858919177427068</v>
+        <v>0.07152659236201764</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2361055348521834</v>
+        <v>0.2971884508050763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1870163382524981</v>
+        <v>0.2621124670638472</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5768781268953186</v>
+        <v>0.4406990821310764</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2963892096281472</v>
+        <v>0.2783950901275779</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2963892096281472</v>
+        <v>0.2783950901275779</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5768781268953186</v>
+        <v>0.4406990821310764</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.768781268953186</v>
+        <v>43.73425350464963</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.768781268953186</v>
+        <v>43.73425350464963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>vquIRDsO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45542.97916666666</v>
+        <v>45549.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,73 +1105,73 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.6408002009637124</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2047774555253603</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.1544223435109274</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.0615978394208716</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4671026151227732</v>
+        <v>0.56217648915498</v>
       </c>
       <c r="R7" t="n">
-        <v>0.260227184233846</v>
+        <v>0.2352924606944046</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2726702006433806</v>
+        <v>0.2025310501506155</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.006779185261923337</v>
+        <v>-0.0786237118087324</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.006779185261923337</v>
+        <v>-0.0786237118087324</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4671026151227732</v>
+        <v>0.56217648915498</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.738818003846966</v>
+        <v>39.11199490849427</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.738818003846966</v>
+        <v>39.11199490849427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>jDDw3kMK</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,86 +1204,86 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5140066820868672</v>
+        <v>0.5210981189628877</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2508352608583912</v>
+        <v>0.2501270971021861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2351580570547417</v>
+        <v>0.2287747839349263</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06311475409836054</v>
+        <v>0.06612466124661243</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3893485902148922</v>
+        <v>0.450123323851813</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2022707830121813</v>
+        <v>0.2138938521733715</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4083806267729265</v>
+        <v>0.3359828239748155</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1732225697181847</v>
+        <v>-0.07097479511107468</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1732225697181847</v>
+        <v>-0.07097479511107468</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4083806267729265</v>
+        <v>0.450123323851813</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.083806267729265</v>
+        <v>30.66729428596038</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.083806267729265</v>
+        <v>30.66729428596038</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,86 +1303,86 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3011272141706924</v>
+        <v>0.3567060741948635</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2745571658615137</v>
+        <v>0.2680391357521402</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4243156199677939</v>
+        <v>0.3752547900529964</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07124374676556844</v>
+        <v>0.06594242259641492</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3106289633555401</v>
+        <v>0.3611920574175471</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2355361087374685</v>
+        <v>0.2913684180020613</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4538349279069915</v>
+        <v>0.3474395245803917</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.02951930793919766</v>
+        <v>0.004485983222683565</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02951930793919766</v>
+        <v>0.004485983222683565</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4538349279069915</v>
+        <v>0.3611920574175471</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.833542358461892</v>
+        <v>29.57773863312472</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.833542358461892</v>
+        <v>29.57773863312472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,86 +1402,86 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.4912899510509645</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.2406061042326519</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.2681039447163835</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.06568475154862607</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3080356206582852</v>
+        <v>0.4269484527460353</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2195141922165861</v>
+        <v>0.2269571303460315</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4724501871251287</v>
+        <v>0.346094416907933</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1107480594655543</v>
+        <v>-0.06434149830492919</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1107480594655543</v>
+        <v>-0.06434149830492919</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4724501871251287</v>
+        <v>0.4269484527460353</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.724501871251287</v>
+        <v>29.32933491503854</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.724501871251287</v>
+        <v>29.32933491503854</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>htYUpyrn</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,86 +1501,86 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3765084473049075</v>
+        <v>0.4640029460504511</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2614641995172969</v>
+        <v>0.2642238998342846</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3620273531777956</v>
+        <v>0.2717731541152641</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06239316239316239</v>
+        <v>0.05129694154084419</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3125887724568495</v>
+        <v>0.3516959887379245</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2433196768276677</v>
+        <v>0.2169160312831512</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4440915507154829</v>
+        <v>0.4313879799789243</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.08206419753768729</v>
+        <v>0.1596148258636602</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.08206419753768729</v>
+        <v>0.1596148258636602</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4440915507154829</v>
+        <v>0.4313879799789243</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.261557482531702</v>
+        <v>42.98112830916207</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.261557482531702</v>
+        <v>42.98112830916207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45549.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1600,86 +1600,86 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5198358413132695</v>
+        <v>0.4484202512371526</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2462380300957592</v>
+        <v>0.2478111914731633</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2339261285909713</v>
+        <v>0.303768557289684</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06871345029239762</v>
+        <v>0.06192901608860857</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4248118716481093</v>
+        <v>0.1183808314516116</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2198265310827618</v>
+        <v>0.2830199750708735</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3553615972691289</v>
+        <v>0.598599193477515</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-0.09502396966516025</v>
+        <v>0.294830636187831</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.09502396966516025</v>
+        <v>0.294830636187831</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4248118716481093</v>
+        <v>0.598599193477515</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3.29787901982949</v>
+        <v>56.50594801321082</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.29787901982949</v>
+        <v>56.50594801321082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45549.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1699,86 +1699,86 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5731605711494815</v>
+        <v>0.383955298343644</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2265348924066998</v>
+        <v>0.2542406705248453</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2003045364438188</v>
+        <v>0.3618040311315107</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05103119243892862</v>
+        <v>0.06304892019177721</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5180211694488097</v>
+        <v>0.4082855259652293</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2243435086214475</v>
+        <v>0.2671428257345124</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2576353219297429</v>
+        <v>0.3245716483002581</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.05513940170067178</v>
+        <v>0.02433022762158532</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.05513940170067178</v>
+        <v>0.02433022762158532</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5180211694488097</v>
+        <v>0.4082855259652293</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4.628817677481379</v>
+        <v>34.99197180601865</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.628817677481379</v>
+        <v>34.99197180601865</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45549.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1798,86 +1798,86 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.6346967559943583</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2087447108603667</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.156558533145275</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.0645645645645645</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3797271155273778</v>
+        <v>0.4504791717800818</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2746597043437124</v>
+        <v>0.1874575299411319</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3456131801289099</v>
+        <v>0.3620632982787864</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.09042213820396555</v>
+        <v>-0.1842175842142765</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.09042213820396555</v>
+        <v>-0.1842175842142765</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3797271155273778</v>
+        <v>0.4504791717800818</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>2.893049773234122</v>
+        <v>21.53647408325075</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.893049773234122</v>
+        <v>21.53647408325075</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45550.84375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1897,86 +1897,86 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3411167512690355</v>
+        <v>0.5865921787709497</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2680203045685279</v>
+        <v>0.2346368715083799</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3908629441624366</v>
+        <v>0.1787709497206704</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06601731601731609</v>
+        <v>0.06547619047619047</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3150329656153589</v>
+        <v>0.5193835625949444</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2351641989709528</v>
+        <v>0.2292449427018279</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4498028354136882</v>
+        <v>0.2513714947032276</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05893989125125165</v>
+        <v>-0.06720861617600526</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>0.05893989125125165</v>
+        <v>-0.06720861617600526</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4498028354136882</v>
+        <v>0.5193835625949444</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.087427266649398</v>
+        <v>36.57401018177289</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.087427266649398</v>
+        <v>36.57401018177289</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>dYUosgsB</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1995,87 +1995,63 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4586948321388156</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2474537910222558</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.2938513768389287</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06346277278562251</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3161732858012471</v>
+        <v>0.320346215891569</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2199821613977584</v>
+        <v>0.1820504418918682</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4638445528009945</v>
+        <v>0.4976033422165628</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>0.1699931759620658</v>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.1699931759620658</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.4638445528009945</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
+        <v>0.5023966577834371</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.638445528009946</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.638445528009946</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>U3Cs29yR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2094,87 +2070,63 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.4605263157894737</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2697368421052631</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2697368421052631</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.0592334494773521</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.299676077465786</v>
+        <v>0.2758681503768786</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1938962583852312</v>
+        <v>0.2927079805588823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5064276641489829</v>
+        <v>0.4314238690642392</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.2366908220437198</v>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.2366908220437198</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.5064276641489829</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.5</v>
-      </c>
+        <v>0.5685761309357608</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>6.064276641489829</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>6.064276641489829</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>vcKjtDdH</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2193,87 +2145,63 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4160475482912332</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.24962852897474</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.3343239227340268</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06825396825396823</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1779266173323399</v>
+        <v>0.1752981286078847</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2052194510738222</v>
+        <v>0.2589367690499624</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6168539315938379</v>
+        <v>0.5657651023421529</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>0.2825300088598112</v>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.2825300088598112</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.6168539315938379</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.8</v>
-      </c>
+        <v>0.4342348976578471</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>7.168539315938379</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.168539315938379</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>Me49cTqr</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2292,87 +2220,63 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.3620273531777956</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2614641995172969</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.3765084473049075</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.06239316239316239</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3629192028742917</v>
+        <v>0.2344459630363376</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2002684583220724</v>
+        <v>0.2540597518997794</v>
       </c>
       <c r="S19" t="n">
-        <v>0.436812338803636</v>
+        <v>0.5114942850638829</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.06030389149872845</v>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.06030389149872845</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>0.436812338803636</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.4885057149361171</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>4.971162303023644</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.971162303023644</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>ImJfuXBN</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45553.88541666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2391,69 +2295,645 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.6516432743439978</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.2039926771859472</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.1443640484700549</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.06568190263842455</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3763672115475741</v>
+        <v>0.3938354168889161</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2687075571057277</v>
+        <v>0.2173473935758442</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3549252313466982</v>
+        <v>0.3888171895352397</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>-0.2752760627964237</v>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
-      <c r="X20" t="n">
-        <v>0.2752760627964237</v>
-      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>0.623632788452426</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.693693693693694</v>
-      </c>
+        <v>0.6061645831110839</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.236327884524259</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.236327884524259</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>0n3Ddmal</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2350894510463274</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3427771047789247</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.422133444174748</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.577866555825252</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM4QZAZp</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3049587197270119</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2438883402323843</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.4511529400406037</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5488470599593963</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>URr9bfCo</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3224838228072021</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2401055926441813</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.4374105845486167</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.5625894154513833</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>QDIbviRT</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.5302740052571996</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1916366835497508</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2780893111930496</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.4697259947428004</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rVnDcERi</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45553.9375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4225626465441834</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.2446057807131378</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3328315727426787</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.5774373534558166</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhnHdYtb</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45553.97916666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.6831675738827819</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.193177711004639</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1236547151125791</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.3168324261172181</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>GroLehd4</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45553.97916666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3206241351700381</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.2564369013669542</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4229389634630077</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.5770610365369923</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YJuQfCBA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45553.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4324074232608325</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2358626399406183</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.3317299367985493</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.5675925767391675</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,50 +613,50 @@
         <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5496329396744335</v>
+        <v>0.5601552393272963</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2278965847430578</v>
+        <v>0.2199223803363519</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2224704755825088</v>
+        <v>0.2199223803363519</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07023297123727534</v>
+        <v>0.05012905855182725</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4064475107721597</v>
+        <v>0.4431382260991653</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2317732046264059</v>
+        <v>0.2210104790605604</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3617792846014344</v>
+        <v>0.3358512948402743</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1431854289022738</v>
+        <v>-0.117017013228131</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1431854289022738</v>
+        <v>-0.117017013228131</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4064475107721597</v>
+        <v>0.4431382260991653</v>
       </c>
       <c r="Z2" t="n">
         <v>1.7</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>21.29386012878101</v>
+        <v>26.37819864744667</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.29386012878101</v>
+        <v>26.37819864744667</v>
       </c>
     </row>
     <row r="3">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -718,44 +718,44 @@
         <v>2.45</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3452849740932643</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2741968911917099</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3805181347150259</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07265128273531629</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2468291676521915</v>
+        <v>0.2557420276080152</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2218764908215194</v>
+        <v>0.2212946528051988</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5312943415262892</v>
+        <v>0.5229633195867859</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1507762068112633</v>
+        <v>0.134052365579319</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1507762068112633</v>
+        <v>0.134052365579319</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5312943415262892</v>
+        <v>0.5229633195867859</v>
       </c>
       <c r="Z3" t="n">
         <v>2.45</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>51.06201893212862</v>
+        <v>50.38816717706551</v>
       </c>
       <c r="AC3" t="n">
-        <v>51.06201893212862</v>
+        <v>50.38816717706551</v>
       </c>
     </row>
     <row r="4">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3752547900529964</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2680391357521402</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3567060741948635</v>
+        <v>0.3398058252427185</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06594242259641492</v>
+        <v>0.05102040816326525</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3418456284354434</v>
+        <v>0.3450967736679375</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2452920074904522</v>
+        <v>0.2209510707687328</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4128623640741045</v>
+        <v>0.4339521555633297</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.05615628987924098</v>
+        <v>0.09414633032061126</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05615628987924098</v>
+        <v>0.09414633032061126</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4128623640741045</v>
+        <v>0.4339521555633297</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>37.93640749224091</v>
+        <v>42.71505874587553</v>
       </c>
       <c r="AC4" t="n">
-        <v>37.93640749224091</v>
+        <v>42.71505874587553</v>
       </c>
     </row>
     <row r="5">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4174185955276579</v>
+        <v>0.4324734446130501</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2471557473519027</v>
+        <v>0.2503793626707132</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3354256571204394</v>
+        <v>0.3171471927162368</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06474519632414366</v>
+        <v>0.05103668261562988</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3110030730157736</v>
+        <v>0.3024582331293043</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2983757453433368</v>
+        <v>0.3127000606021945</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3906211816408898</v>
+        <v>0.3848417062685012</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.05519552452045035</v>
+        <v>0.06769451355226441</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05519552452045035</v>
+        <v>0.06769451355226441</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3906211816408898</v>
+        <v>0.3848417062685012</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>36.05972617342332</v>
+        <v>36.60323165275762</v>
       </c>
       <c r="AC5" t="n">
-        <v>36.05972617342332</v>
+        <v>36.60323165275762</v>
       </c>
     </row>
     <row r="6">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6221653026800774</v>
+        <v>0.6611981108625404</v>
       </c>
       <c r="M6" t="n">
-        <v>0.215530705316424</v>
+        <v>0.2018394233159334</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1623039920034985</v>
+        <v>0.1369624658215262</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07152659236201764</v>
+        <v>0.04303863106040962</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2971884508050763</v>
+        <v>0.2878139317932192</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2621124670638472</v>
+        <v>0.2340678510062117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4406990821310764</v>
+        <v>0.4781182172005691</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2783950901275779</v>
+        <v>0.3411557513790429</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2783950901275779</v>
+        <v>0.3411557513790429</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4406990821310764</v>
+        <v>0.4781182172005691</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>43.73425350464963</v>
+        <v>46.76088697442348</v>
       </c>
       <c r="AC6" t="n">
-        <v>43.73425350464963</v>
+        <v>46.76088697442348</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K7" t="n">
         <v>6.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6408002009637124</v>
+        <v>0.6510138740661685</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2047774555253603</v>
+        <v>0.1953041622198506</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1544223435109274</v>
+        <v>0.1536819637139808</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0615978394208716</v>
+        <v>0.06671220400728606</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.56217648915498</v>
+        <v>0.5785013575249965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2352924606944046</v>
+        <v>0.2132185601627871</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2025310501506155</v>
+        <v>0.2082800823122163</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.0786237118087324</v>
+        <v>-0.07251251654117197</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0786237118087324</v>
+        <v>-0.07251251654117197</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.56217648915498</v>
+        <v>0.5785013575249965</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>39.11199490849427</v>
+        <v>40.92672795909408</v>
       </c>
       <c r="AC7" t="n">
-        <v>39.11199490849427</v>
+        <v>40.92672795909408</v>
       </c>
     </row>
     <row r="8">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5210981189628877</v>
+        <v>0.4949762030671602</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2501270971021861</v>
+        <v>0.2626123744050767</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2287747839349263</v>
+        <v>0.2424114225277631</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06612466124661243</v>
+        <v>0.05774824361211794</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.450123323851813</v>
+        <v>0.4652730549050518</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2138938521733715</v>
+        <v>0.1957919430398784</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3359828239748155</v>
+        <v>0.3389350020550699</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.07097479511107468</v>
+        <v>-0.02970314816210845</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.07097479511107468</v>
+        <v>-0.02970314816210845</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.450123323851813</v>
+        <v>0.4652730549050518</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>30.66729428596038</v>
+        <v>35.23091743639124</v>
       </c>
       <c r="AC8" t="n">
-        <v>30.66729428596038</v>
+        <v>35.23091743639124</v>
       </c>
     </row>
     <row r="9">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3567060741948635</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2680391357521402</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3752547900529964</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06594242259641492</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3611920574175471</v>
+        <v>0.3704035014766095</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2913684180020613</v>
+        <v>0.2718248096815127</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3474395245803917</v>
+        <v>0.3577716888418779</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.004485983222683565</v>
+        <v>0.01988803755908375</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004485983222683565</v>
+        <v>0.01988803755908375</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3611920574175471</v>
+        <v>0.3704035014766095</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>29.57773863312472</v>
+        <v>31.56859272191064</v>
       </c>
       <c r="AC9" t="n">
-        <v>29.57773863312472</v>
+        <v>31.56859272191064</v>
       </c>
     </row>
     <row r="10">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4912899510509645</v>
+        <v>0.5293737895416398</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2406061042326519</v>
+        <v>0.2382182052937379</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2681039447163835</v>
+        <v>0.2324080051646223</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06568475154862607</v>
+        <v>0.04945799457994582</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4269484527460353</v>
+        <v>0.4620513988290332</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2269571303460315</v>
+        <v>0.2138321175044229</v>
       </c>
       <c r="S10" t="n">
-        <v>0.346094416907933</v>
+        <v>0.324116483666544</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.06434149830492919</v>
+        <v>-0.06732239071260665</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.06434149830492919</v>
+        <v>-0.06732239071260665</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4269484527460353</v>
+        <v>0.4620513988290332</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>29.32933491503854</v>
+        <v>31.92751583480172</v>
       </c>
       <c r="AC10" t="n">
-        <v>29.32933491503854</v>
+        <v>31.92751583480172</v>
       </c>
     </row>
     <row r="11">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3516959887379245</v>
+        <v>0.365465189326119</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2169160312831512</v>
+        <v>0.2035711323780466</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4313879799789243</v>
+        <v>0.4309636782958344</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1596148258636602</v>
+        <v>0.1678057835589923</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1596148258636602</v>
+        <v>0.1678057835589923</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4313879799789243</v>
+        <v>0.4309636782958344</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>42.98112830916207</v>
+        <v>42.94680881799969</v>
       </c>
       <c r="AC11" t="n">
-        <v>42.98112830916207</v>
+        <v>42.94680881799969</v>
       </c>
     </row>
     <row r="12">
@@ -1600,56 +1600,56 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4484202512371526</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2478111914731633</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="N12" t="n">
-        <v>0.303768557289684</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06192901608860857</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1183808314516116</v>
+        <v>0.1028890837823758</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2830199750708735</v>
+        <v>0.2876250021256304</v>
       </c>
       <c r="S12" t="n">
-        <v>0.598599193477515</v>
+        <v>0.6094859140919937</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.294830636187831</v>
+        <v>0.3452723299171424</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0.294830636187831</v>
+        <v>0.3452723299171424</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.598599193477515</v>
+        <v>0.6094859140919937</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>56.50594801321082</v>
+        <v>57.38651654924633</v>
       </c>
       <c r="AC12" t="n">
-        <v>56.50594801321082</v>
+        <v>57.38651654924633</v>
       </c>
     </row>
     <row r="13">
@@ -1699,56 +1699,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="L13" t="n">
-        <v>0.383955298343644</v>
+        <v>0.3531359563693027</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2542406705248453</v>
+        <v>0.2576938059992208</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3618040311315107</v>
+        <v>0.3891702376314764</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06304892019177721</v>
+        <v>0.04880390594676309</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4082855259652293</v>
+        <v>0.4351922636732301</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2671428257345124</v>
+        <v>0.2684016211823131</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3245716483002581</v>
+        <v>0.2964061151444568</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.02433022762158532</v>
+        <v>0.08205630730392743</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02433022762158532</v>
+        <v>0.08205630730392743</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4082855259652293</v>
+        <v>0.4351922636732301</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>34.99197180601865</v>
+        <v>41.83746722645417</v>
       </c>
       <c r="AC13" t="n">
-        <v>34.99197180601865</v>
+        <v>41.83746722645417</v>
       </c>
     </row>
     <row r="14">
@@ -1801,50 +1801,50 @@
         <v>1.48</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6346967559943583</v>
+        <v>0.6417473541995046</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2087447108603667</v>
+        <v>0.1999549650979509</v>
       </c>
       <c r="N14" t="n">
-        <v>0.156558533145275</v>
+        <v>0.1582976807025445</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0645645645645645</v>
+        <v>0.05286865813181607</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4504791717800818</v>
+        <v>0.4056433277857615</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1874575299411319</v>
+        <v>0.2228873484035309</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3620632982787864</v>
+        <v>0.3714693238107076</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.1842175842142765</v>
+        <v>-0.2361040264137431</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1842175842142765</v>
+        <v>-0.2361040264137431</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4504791717800818</v>
+        <v>0.4056433277857615</v>
       </c>
       <c r="Z14" t="n">
         <v>1.48</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>21.53647408325075</v>
+        <v>13.71312626605787</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.53647408325075</v>
+        <v>13.71312626605787</v>
       </c>
     </row>
     <row r="15">
@@ -1897,56 +1897,56 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5865921787709497</v>
+        <v>0.6080529945374101</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2346368715083799</v>
+        <v>0.232839805225301</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1787709497206704</v>
+        <v>0.159107200237289</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06547619047619047</v>
+        <v>0.04751178085029251</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5193835625949444</v>
+        <v>0.5537124813524965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2292449427018279</v>
+        <v>0.2020209339522145</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2513714947032276</v>
+        <v>0.2442665846952888</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.06720861617600526</v>
+        <v>-0.05434051318491362</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.06720861617600526</v>
+        <v>-0.05434051318491362</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5193835625949444</v>
+        <v>0.5537124813524965</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1954,986 +1954,11 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>36.57401018177289</v>
+        <v>40.39152454796015</v>
       </c>
       <c r="AC15" t="n">
-        <v>36.57401018177289</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>inter miami</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>167</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.320346215891569</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1820504418918682</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4976033422165628</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="n">
-        <v>0.5023966577834371</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>new england revolution</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>167</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.2758681503768786</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.2927079805588823</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.4314238690642392</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="n">
-        <v>0.5685761309357608</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>167</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1752981286078847</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2589367690499624</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.5657651023421529</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="n">
-        <v>0.4342348976578471</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>columbus crew</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>167</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2344459630363376</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2540597518997794</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.5114942850638829</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="n">
-        <v>0.4885057149361171</v>
-      </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45553.88541666666</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>charlotte</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>167</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.3938354168889161</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.2173473935758442</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.3888171895352397</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>0.6061645831110839</v>
-      </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>167</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2350894510463274</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.3427771047789247</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.422133444174748</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="n">
-        <v>0.577866555825252</v>
-      </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>fc cincinnati</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>167</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.3049587197270119</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2438883402323843</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.4511529400406037</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="n">
-        <v>0.5488470599593963</v>
-      </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>167</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.3224838228072021</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.2401055926441813</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.4374105845486167</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="n">
-        <v>0.5625894154513833</v>
-      </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>167</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.5302740052571996</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.1916366835497508</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.2780893111930496</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="n">
-        <v>0.4697259947428004</v>
-      </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45553.9375</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>167</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.4225626465441834</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.2446057807131378</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.3328315727426787</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="n">
-        <v>0.5774373534558166</v>
-      </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>167</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.6831675738827819</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.193177711004639</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.1236547151125791</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="n">
-        <v>0.3168324261172181</v>
-      </c>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>167</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.3206241351700381</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.2564369013669542</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.4229389634630077</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="n">
-        <v>0.5770610365369923</v>
-      </c>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>167</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.4324074232608325</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.2358626399406183</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.3317299367985493</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="n">
-        <v>0.5675925767391675</v>
-      </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
+        <v>40.39152454796015</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5601552393272963</v>
+        <v>0.3692307692307692</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2199223803363519</v>
+        <v>0.2615384615384615</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2199223803363519</v>
+        <v>0.3692307692307692</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05012905855182725</v>
+        <v>0.06209150326797408</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4431382260991653</v>
+        <v>0.1822950585492632</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2210104790605604</v>
+        <v>0.4963222306685307</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3358512948402743</v>
+        <v>0.3213827107822061</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.117017013228131</v>
+        <v>0.2347837691300692</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.117017013228131</v>
+        <v>0.2347837691300692</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4431382260991653</v>
+        <v>0.4963222306685307</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>26.37819864744667</v>
+        <v>1.192644461337061</v>
       </c>
       <c r="AC2" t="n">
-        <v>26.37819864744667</v>
+        <v>1.192644461337061</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.5622942825795441</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2290320614409362</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.2086736559795196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.06492705645619345</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2557420276080152</v>
+        <v>0.6395407023278042</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2212946528051988</v>
+        <v>0.2206797374774311</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5229633195867859</v>
+        <v>0.1397795601947647</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.134052365579319</v>
+        <v>0.07724641974826019</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.134052365579319</v>
+        <v>0.07724641974826019</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5229633195867859</v>
+        <v>0.6395407023278042</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>50.38816717706551</v>
+        <v>1.433574244152129</v>
       </c>
       <c r="AC3" t="n">
-        <v>50.38816717706551</v>
+        <v>1.433574244152129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,68 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3883495145631068</v>
+        <v>0.4059040590405905</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2718446601941747</v>
+        <v>0.2829028290282903</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3398058252427185</v>
+        <v>0.3111931119311193</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05102040816326525</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.3450967736679375</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2209510707687328</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.4339521555633297</v>
-      </c>
+        <v>0.07114624505928857</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.09414633032061126</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.09414633032061126</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.4339521555633297</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>2.8</v>
+        <v>1.30188679245283</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>42.71505874587553</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>42.71505874587553</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +889,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4324734446130501</v>
+        <v>0.5420741468672235</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2503793626707132</v>
+        <v>0.2604967428000824</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3171471927162368</v>
+        <v>0.197429110332694</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05103668261562988</v>
+        <v>0.06633877564817636</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3024582331293043</v>
+        <v>0.4106405582685528</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3127000606021945</v>
+        <v>0.1016616347514556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3848417062685012</v>
+        <v>0.4876978069799915</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06769451355226441</v>
+        <v>0.2902686966472975</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06769451355226441</v>
+        <v>0.2902686966472975</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3848417062685012</v>
+        <v>0.4876978069799915</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +946,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>36.60323165275762</v>
+        <v>1.175395613959983</v>
       </c>
       <c r="AC5" t="n">
-        <v>36.60323165275762</v>
+        <v>1.175395613959983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +988,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.75</v>
       </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.6611981108625404</v>
+        <v>0.5521115846571096</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2018394233159334</v>
+        <v>0.2502905850445564</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1369624658215262</v>
+        <v>0.197597830298334</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04303863106040962</v>
+        <v>0.06542827657378747</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2878139317932192</v>
+        <v>0.6390174151579789</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2340678510062117</v>
+        <v>0.104510126050308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4781182172005691</v>
+        <v>0.2564724587917129</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3411557513790429</v>
+        <v>0.08690583050086931</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3411557513790429</v>
+        <v>0.08690583050086931</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4781182172005691</v>
+        <v>0.6390174151579789</v>
       </c>
       <c r="Z6" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1045,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>46.76088697442348</v>
+        <v>1.451846491317696</v>
       </c>
       <c r="AC6" t="n">
-        <v>46.76088697442348</v>
+        <v>1.451846491317696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1087,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6.1</v>
+        <v>2.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6510138740661685</v>
+        <v>0.3452849740932643</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1953041622198506</v>
+        <v>0.2741968911917099</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1536819637139808</v>
+        <v>0.3805181347150259</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06671220400728606</v>
+        <v>0.07265128273531629</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5785013575249965</v>
+        <v>0.6248715650520207</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2132185601627871</v>
+        <v>0.09453658779240379</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2082800823122163</v>
+        <v>0.2805918471555755</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.07251251654117197</v>
+        <v>0.2795865909587564</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.07251251654117197</v>
+        <v>0.2795865909587564</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5785013575249965</v>
+        <v>0.6248715650520207</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1144,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>40.92672795909408</v>
+        <v>1.449743130104041</v>
       </c>
       <c r="AC7" t="n">
-        <v>40.92672795909408</v>
+        <v>1.449743130104041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1186,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4949762030671602</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2626123744050767</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2424114225277631</v>
+        <v>0.4276704769412692</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05774824361211794</v>
+        <v>0.06284038542103065</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4652730549050518</v>
+        <v>0.1030713040601068</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1957919430398784</v>
+        <v>0.4671978289500065</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3389350020550699</v>
+        <v>0.4297308669898868</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.02970314816210845</v>
+        <v>0.1983763863012087</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02970314816210845</v>
+        <v>0.1983763863012087</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4652730549050518</v>
+        <v>0.4671978289500065</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1243,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>35.23091743639124</v>
+        <v>1.134395657900013</v>
       </c>
       <c r="AC8" t="n">
-        <v>35.23091743639124</v>
+        <v>1.134395657900013</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1285,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3154977102916365</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2868161002651242</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3976861894432394</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05653170359052706</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3704035014766095</v>
+        <v>0.1227143443875491</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2718248096815127</v>
+        <v>0.2014761860978063</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3577716888418779</v>
+        <v>0.6758094695146445</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.01988803755908375</v>
+        <v>0.2781232800714051</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01988803755908375</v>
+        <v>0.2781232800714051</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3704035014766095</v>
+        <v>0.6758094695146445</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1342,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>31.56859272191064</v>
+        <v>1.551618939029289</v>
       </c>
       <c r="AC9" t="n">
-        <v>31.56859272191064</v>
+        <v>1.551618939029289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1384,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5293737895416398</v>
+        <v>0.4866595517609391</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2382182052937379</v>
+        <v>0.2497331910352187</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2324080051646223</v>
+        <v>0.263607257203842</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04945799457994582</v>
+        <v>0.05375618533513293</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4620513988290332</v>
+        <v>0.4907907967039264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2138321175044229</v>
+        <v>0.2216899510330607</v>
       </c>
       <c r="S10" t="n">
-        <v>0.324116483666544</v>
+        <v>0.2875192522630129</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.06732239071260665</v>
+        <v>0.004131244942987333</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.06732239071260665</v>
+        <v>0.004131244942987333</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4620513988290332</v>
+        <v>0.4907907967039264</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1441,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>31.92751583480172</v>
+        <v>0.9898440832938276</v>
       </c>
       <c r="AC10" t="n">
-        <v>31.92751583480172</v>
+        <v>0.9898440832938276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1483,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5441860465116279</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.244186046511628</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2116279069767442</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05006105006104988</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.365465189326119</v>
+        <v>0.3109718141450994</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2035711323780466</v>
+        <v>0.2464263460786007</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4309636782958344</v>
+        <v>0.4426018397762999</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1678057835589923</v>
+        <v>0.2309739327995557</v>
       </c>
       <c r="W11" t="n">
         <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1678057835589923</v>
+        <v>0.2309739327995557</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4309636782958344</v>
+        <v>0.4426018397762999</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,24 +1540,24 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>42.94680881799969</v>
+        <v>1.0852036795526</v>
       </c>
       <c r="AC11" t="n">
-        <v>42.94680881799969</v>
+        <v>1.0852036795526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45556.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1600,56 +1582,56 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4979941900677826</v>
+        <v>0.5231388329979879</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2377922257573662</v>
+        <v>0.2354124748490946</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2642135841748513</v>
+        <v>0.2414486921529175</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05133798720186156</v>
+        <v>0.06196581196581197</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1028890837823758</v>
+        <v>0.2796932191597262</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2876250021256304</v>
+        <v>0.2198044841264083</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6094859140919937</v>
+        <v>0.5005022967138655</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3452723299171424</v>
+        <v>0.2590536045609479</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3452723299171424</v>
+        <v>0.2590536045609479</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.6094859140919937</v>
+        <v>0.5005022967138655</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1657,20 +1639,20 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>57.38651654924633</v>
+        <v>1.201004593427731</v>
       </c>
       <c r="AC12" t="n">
-        <v>57.38651654924633</v>
+        <v>1.201004593427731</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1679,7 +1661,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1699,56 +1681,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3531359563693027</v>
+        <v>0.5112910097997443</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2576938059992208</v>
+        <v>0.2522368981678739</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3891702376314764</v>
+        <v>0.2364720920323818</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04880390594676309</v>
+        <v>0.05720720720720718</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4351922636732301</v>
+        <v>0.2793579768250165</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2684016211823131</v>
+        <v>0.2687758618512388</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2964061151444568</v>
+        <v>0.4518661613237449</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.08205630730392743</v>
+        <v>0.2153940692913631</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>0.08205630730392743</v>
+        <v>0.2153940692913631</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4351922636732301</v>
+        <v>0.4518661613237449</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1756,29 +1738,29 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>41.83746722645417</v>
+        <v>1.10373232264749</v>
       </c>
       <c r="AC13" t="n">
-        <v>41.83746722645417</v>
+        <v>1.10373232264749</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1798,56 +1780,56 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6417473541995046</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1999549650979509</v>
+        <v>0.2499999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1582976807025445</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05286865813181607</v>
+        <v>0.06666666666666687</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4056433277857615</v>
+        <v>0.705192031378164</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2228873484035309</v>
+        <v>0.05028138525710329</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3714693238107076</v>
+        <v>0.2445265833647326</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.2361040264137431</v>
+        <v>0.3301920313781641</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2361040264137431</v>
+        <v>0.3301920313781641</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4056433277857615</v>
+        <v>0.705192031378164</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1855,109 +1837,10 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>13.71312626605787</v>
+        <v>1.610384062756328</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.71312626605787</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45550.84375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>167</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.6080529945374101</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.232839805225301</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.159107200237289</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.04751178085029251</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5537124813524965</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.2020209339522145</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2442665846952888</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.05434051318491362</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.05434051318491362</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.5537124813524965</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>40.39152454796015</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>40.39152454796015</v>
+        <v>1.610384062756328</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/predicciones.xlsx
+++ b/data/usa/p6_deployment/predicciones.xlsx
@@ -510,12 +510,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_0</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45556.625</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,77 +610,75 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3692307692307692</v>
+        <v>0.3937947494033414</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2615384615384615</v>
+        <v>0.2625298329355609</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3692307692307692</v>
+        <v>0.3436754176610979</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06209150326797408</v>
+        <v>0.05808080808080796</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1822950585492632</v>
+        <v>0.2476448267698288</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4963222306685307</v>
+        <v>0.3268080949783325</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3213827107822061</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4255470931529999</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2347837691300692</v>
+        <v>0.081871675491902</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2347837691300692</v>
+        <v>0.081871675491902</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4963222306685307</v>
+        <v>0.4255470931529999</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.192644461337061</v>
+        <v>3.404376745223999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.192644461337061</v>
+        <v>3.404376745223999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.70833333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -689,7 +687,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +707,84 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5622942825795441</v>
+        <v>0.556367975035947</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2290320614409362</v>
+        <v>0.2251965613240738</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2086736559795196</v>
+        <v>0.2184354636399792</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06492705645619345</v>
+        <v>0.05727741442997525</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6395407023278042</v>
+        <v>0.1969160884618759</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2206797374774311</v>
+        <v>0.5568646192550659</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1397795601947647</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2462192177772522</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.07724641974826019</v>
+        <v>0.0004966442191188802</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07724641974826019</v>
+        <v>0.0004966442191188802</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6395407023278042</v>
+        <v>0.5568646192550659</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.433574244152129</v>
+        <v>4.454916954040527</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.433574244152129</v>
+        <v>4.454916954040527</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>llHizuVJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,63 +804,79 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4059040590405905</v>
+        <v>0.5461537278306747</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2829028290282903</v>
+        <v>0.2207318761440371</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3111931119311193</v>
+        <v>0.2331143960252881</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07114624505928857</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
+        <v>0.04627789267005178</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3560613691806793</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3010477125644684</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3428908586502075</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.1353294930366422</v>
+      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0.1353294930366422</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3560613691806793</v>
+      </c>
       <c r="Z4" t="n">
-        <v>1.30188679245283</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.848490953445435</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.848490953445435</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -889,86 +901,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5420741468672235</v>
+        <v>0.4411346172089934</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2604967428000824</v>
+        <v>0.2529171805331563</v>
       </c>
       <c r="N5" t="n">
-        <v>0.197429110332694</v>
+        <v>0.3059482022578503</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06633877564817636</v>
+        <v>0.05436359089772447</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4106405582685528</v>
+        <v>0.2494526952505112</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1016616347514556</v>
+        <v>0.4446759819984436</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4876978069799915</v>
+        <v>0.3058713674545288</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2902686966472975</v>
+        <v>0.003541364789450163</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2902686966472975</v>
+        <v>0.003541364789450163</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4876978069799915</v>
+        <v>0.4446759819984436</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1.175395613959983</v>
+        <v>3.557407855987549</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.175395613959983</v>
+        <v>3.557407855987549</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -988,86 +1000,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5521115846571096</v>
+        <v>0.3955802383431679</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2502905850445564</v>
+        <v>0.2434339928265649</v>
       </c>
       <c r="N6" t="n">
-        <v>0.197597830298334</v>
+        <v>0.3609857688302673</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06542827657378747</v>
+        <v>0.05330505995905233</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6390174151579789</v>
+        <v>0.3115589916706085</v>
       </c>
       <c r="R6" t="n">
-        <v>0.104510126050308</v>
+        <v>0.3146456778049469</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2564724587917129</v>
+        <v>0.3737953901290894</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.08690583050086931</v>
+        <v>0.01280962129882207</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08690583050086931</v>
+        <v>0.01280962129882207</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6390174151579789</v>
+        <v>0.3737953901290894</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>1.451846491317696</v>
+        <v>2.990363121032715</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.451846491317696</v>
+        <v>2.990363121032715</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1087,81 +1099,79 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3452849740932643</v>
+        <v>0.5324675324675325</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2741968911917099</v>
+        <v>0.2337662337662338</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3805181347150259</v>
+        <v>0.2337662337662338</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07265128273531629</v>
+        <v>0.04336043360433606</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6248715650520207</v>
+        <v>0.270222008228302</v>
       </c>
       <c r="R7" t="n">
-        <v>0.09453658779240379</v>
+        <v>0.4628515541553497</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2805918471555755</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2669263482093811</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2795865909587564</v>
+        <v>-0.0696159783121828</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2795865909587564</v>
+        <v>-0.0696159783121828</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6248715650520207</v>
+        <v>0.4628515541553497</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.449743130104041</v>
+        <v>3.145884606745335</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.449743130104041</v>
+        <v>3.145884606745335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1186,86 +1196,86 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.303508080409933</v>
+        <v>0.3291753291753292</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2688214426487978</v>
+        <v>0.2494802494802495</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4276704769412692</v>
+        <v>0.4213444213444213</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06284038542103065</v>
+        <v>0.05482456140350878</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1030713040601068</v>
+        <v>0.3269728124141693</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4671978289500065</v>
+        <v>0.3468203246593475</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4297308669898868</v>
+        <v>0.3262069225311279</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1983763863012087</v>
+        <v>0.01764499548401838</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1983763863012087</v>
+        <v>0.01764499548401838</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4671978289500065</v>
+        <v>0.3468203246593475</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.134395657900013</v>
+        <v>2.77456259727478</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.134395657900013</v>
+        <v>2.77456259727478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1285,86 +1295,86 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3154977102916365</v>
+        <v>0.3543534856812265</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2868161002651242</v>
+        <v>0.2551345096904831</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3976861894432394</v>
+        <v>0.3905120046282904</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05653170359052706</v>
+        <v>0.04520030234315953</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1227143443875491</v>
+        <v>0.2603981196880341</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2014761860978063</v>
+        <v>0.2848783433437347</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6758094695146445</v>
+        <v>0.4547235071659088</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2781232800714051</v>
+        <v>0.06421150253761843</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2781232800714051</v>
+        <v>0.06421150253761843</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6758094695146445</v>
+        <v>0.4547235071659088</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.551618939029289</v>
+        <v>3.637788057327271</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.551618939029289</v>
+        <v>3.637788057327271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.9375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1384,86 +1394,86 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4866595517609391</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2497331910352187</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="N10" t="n">
-        <v>0.263607257203842</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05375618533513293</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4907907967039264</v>
+        <v>0.3052732348442078</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2216899510330607</v>
+        <v>0.221908837556839</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2875192522630129</v>
+        <v>0.4728179275989532</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.004131244942987333</v>
+        <v>0.1067120532005124</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004131244942987333</v>
+        <v>0.1067120532005124</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4907907967039264</v>
+        <v>0.4728179275989532</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.9898440832938276</v>
+        <v>3.782543420791626</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9898440832938276</v>
+        <v>3.782543420791626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1483,86 +1493,88 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5441860465116279</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="M11" t="n">
-        <v>0.244186046511628</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2116279069767442</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05006105006104988</v>
+        <v>0.04761904761904745</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3109718141450994</v>
+        <v>0.2200533598661423</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2464263460786007</v>
+        <v>0.5411854386329651</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4426018397762999</v>
+        <v>0.2387612015008926</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
       <c r="V11" t="n">
-        <v>0.2309739327995557</v>
+        <v>-0.09517819773067138</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2309739327995557</v>
+        <v>-0.09517819773067138</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4426018397762999</v>
+        <v>0.5411854386329651</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>1.0852036795526</v>
+        <v>3.56805792721835</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.0852036795526</v>
+        <v>3.56805792721835</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1582,86 +1594,86 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5231388329979879</v>
+        <v>0.3179297597042514</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2354124748490946</v>
+        <v>0.2384473197781886</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2414486921529175</v>
+        <v>0.4436229205175601</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06196581196581197</v>
+        <v>0.04844961240310064</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2796932191597262</v>
+        <v>0.2624878883361816</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2198044841264083</v>
+        <v>0.3565721809864044</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5005022967138655</v>
+        <v>0.3809398412704468</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2590536045609479</v>
+        <v>-0.06268307924711336</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2590536045609479</v>
+        <v>-0.06268307924711336</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5005022967138655</v>
+        <v>0.3809398412704468</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>1.201004593427731</v>
+        <v>2.546054096186667</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.201004593427731</v>
+        <v>2.546054096186667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.70833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1681,86 +1693,86 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5112910097997443</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2522368981678739</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2364720920323818</v>
+        <v>0.1636363636363637</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05720720720720718</v>
+        <v>0.06280193236714959</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2793579768250165</v>
+        <v>0.2683462500572205</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2687758618512388</v>
+        <v>0.4143373668193817</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4518661613237449</v>
+        <v>0.3173163831233978</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2153940692913631</v>
+        <v>-0.2129353604533456</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2153940692913631</v>
+        <v>-0.2129353604533456</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4518661613237449</v>
+        <v>0.4143373668193817</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>1.10373232264749</v>
+        <v>1.611216050928289</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.10373232264749</v>
+        <v>1.611216050928289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.83333333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1780,67 +1792,67 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3749999999999999</v>
+        <v>0.6229605458320973</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2499999999999999</v>
+        <v>0.1931177692079502</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3749999999999999</v>
+        <v>0.1839216849599525</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06666666666666687</v>
+        <v>0.03563748079877116</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.705192031378164</v>
+        <v>0.2832965850830078</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05028138525710329</v>
+        <v>0.4666794240474701</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2445265833647326</v>
+        <v>0.2500239908695221</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3301920313781641</v>
+        <v>-0.1562811217846272</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3301920313781641</v>
+        <v>-0.1562811217846272</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.705192031378164</v>
+        <v>0.4666794240474701</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>1.610384062756328</v>
+        <v>2.483186418102743</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.610384062756328</v>
+        <v>2.483186418102743</v>
       </c>
     </row>
   </sheetData>
